--- a/docs/FEATURE_STATUS_2026-10-08.xlsx
+++ b/docs/FEATURE_STATUS_2026-10-08.xlsx
@@ -20,7 +20,7 @@
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Features'!$A$1:$P$416</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ATIP Waves'!$A$1:$G$46</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Branches!$A$1:$I$75</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Pull Requests'!$A$1:$J$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Pull Requests'!$A$1:$J$26</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7335" uniqueCount="2140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7344" uniqueCount="2134">
   <si>
     <t xml:space="preserve">Feature and merge status - ATIP-DEV, bkesari, bkesari-platform</t>
   </si>
@@ -94,10 +94,10 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">638d600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge pull request #10: record that this repo and GoKesari have diverged</t>
+    <t xml:space="preserve">3cfd098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merge pull request #13: fill blank test secrets too, so tests pass after cp .env.example .env</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari</t>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">Read this first</t>
   </si>
   <si>
-    <t xml:space="preserve">1. All five PRs that were open on 2026-10-08 (ATIP-DEV#8, bkesari#9 and #10, bkesari-platform#1 and #2) are now merged. Still open: bkesari#12 (admin dashboard fix, opened by another session), bkesari#13 (a test fix), and the bkesari-platform PR with the local MySQL script.</t>
+    <t xml:space="preserve">1. All five PRs that were open on 2026-10-08 (ATIP-DEV#8, bkesari#9 and #10, bkesari-platform#1 and #2) are now merged. Since then bkesari#12 and #13 were merged too (2026-10-09), and this workbook arrived with bkesari-platform#4. No pull request is open in any of the three repos.</t>
   </si>
   <si>
     <t xml:space="preserve">2. 'Local Git (fresh clone)' is the clone this report was built from, which matches GitHub. It cannot see commits that exist only on your Mac. Run tools/check_local_git.sh on the Mac to list those (see MAC_DEPLOYMENT.md).</t>
@@ -4609,7 +4609,7 @@
     <t xml:space="preserve">claude/amazing-cannon-5n3fro</t>
   </si>
   <si>
-    <t xml:space="preserve">PASS - 281/281 on MySQL with PR #13 (CI green)</t>
+    <t xml:space="preserve">PASS - 284/284 on MySQL (CI green)</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari/pull/9</t>
@@ -4669,19 +4669,7 @@
     <t xml:space="preserve">claude/epic-brown-iurf1w</t>
   </si>
   <si>
-    <t xml:space="preserve">Draft PR - not merged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only on branch claude/epic-brown-iurf1w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IN REVIEW (draft PR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASS - 281/281 on MySQL (270/281 before); typecheck, eslint clean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review, then merge or close PR #13</t>
+    <t xml:space="preserve">PASS - 284/284 on MySQL, also with a .env copied from .env.example (CI green)</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari/pull/13</t>
@@ -4702,15 +4690,6 @@
     <t xml:space="preserve">claude/charming-edison-ofoncf</t>
   </si>
   <si>
-    <t xml:space="preserve">Only on branch claude/charming-edison-ofoncf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Its author reports 284/284 on MySQL 8.0.46; not re-run here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review, then merge. Conflicts with PR #13 in tests/setup.ts (keep both changes)</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari/pull/12</t>
   </si>
   <si>
@@ -5395,16 +5374,16 @@
     <t xml:space="preserve">tools/setup_local_mysql.sh: one database + user per site on the Mac's MySQL, writes each app's .env, runs migrations, seeds empty databases; safe to re-run</t>
   </si>
   <si>
-    <t xml:space="preserve">pull request opened with this workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASS - fresh run and re-run against MySQL 8.0; all three sites then served from it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review, then merge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari-platform/pulls</t>
+    <t xml:space="preserve">PR #4 (arrived with this workbook)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS - fresh run and re-run against MySQL 8.0; all three sites then served from it (CI green)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run it once on the Mac: tools/setup_local_mysql.sh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari-platform/pull/4</t>
   </si>
   <si>
     <t xml:space="preserve">Wave</t>
@@ -5995,6 +5974,9 @@
     <t xml:space="preserve">https://github.com/sanjaymorankar-debug/bkesari/pull/1</t>
   </si>
   <si>
+    <t xml:space="preserve">Local MySQL setup script, and the Mac guide and status workbook brought up to date</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mac setup guide, cross-repo feature status workbook, and a local Git checker</t>
   </si>
   <si>
@@ -6274,7 +6256,7 @@
     <t xml:space="preserve">#10 merged</t>
   </si>
   <si>
-    <t xml:space="preserve">#12 draft, #11 merged, #8 merged</t>
+    <t xml:space="preserve">#12 merged, #11 merged, #8 merged</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-01</t>
@@ -6343,7 +6325,7 @@
     <t xml:space="preserve">npm test against bk_milk_test</t>
   </si>
   <si>
-    <t xml:space="preserve">270/281 with .env from .env.example: 11 geocoding tests fail because tests/setup.ts keeps a blank GOOGLE_MAPS_SERVER_API_KEY. With PR #13: 281/281. typecheck and eslint clean</t>
+    <t xml:space="preserve">PASS: 284/284 on main with #12 and #13 merged, both with the setup script's .env and with a .env copied from .env.example (before #13: 270/281). typecheck clean, eslint 0 errors</t>
   </si>
   <si>
     <t xml:space="preserve">npm run dev</t>
@@ -7272,15 +7254,15 @@
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A13,'All Features'!$I$2:$I$416,"Yes")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A13,'All Features'!$I$2:$I$416,"No")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A13,'All Features'!$L$2:$L$416,"COMPLETED")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A13,'All Features'!$L$2:$L$416,"IMPLEMENTED BUT NOT VERIFIED")</f>
@@ -7300,7 +7282,7 @@
       </c>
       <c r="J13" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A13,'All Features'!$L$2:$L$416,"IN REVIEW (draft PR)")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A13,'All Features'!$L$2:$L$416,"SUPERSEDED")</f>
@@ -7321,15 +7303,15 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A14,'All Features'!$I$2:$I$416,"Yes")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A14,'All Features'!$I$2:$I$416,"No")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A14,'All Features'!$L$2:$L$416,"COMPLETED")</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A14,'All Features'!$L$2:$L$416,"IMPLEMENTED BUT NOT VERIFIED")</f>
@@ -7349,7 +7331,7 @@
       </c>
       <c r="J14" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A14,'All Features'!$L$2:$L$416,"IN REVIEW (draft PR)")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="8" t="n">
         <f aca="false">COUNTIFS('All Features'!$A$2:$A$416,$A14,'All Features'!$L$2:$L$416,"SUPERSEDED")</f>
@@ -7370,15 +7352,15 @@
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">SUM(C12:C14)</f>
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">SUM(D12:D14)</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">SUM(E12:E14)</f>
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">SUM(F12:F14)</f>
@@ -7398,7 +7380,7 @@
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">SUM(J12:J14)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">SUM(K12:K14)</f>
@@ -7445,19 +7427,19 @@
         <v>10</v>
       </c>
       <c r="B20" s="8" t="n">
-        <f aca="false">COUNTIF('Pull Requests'!$A$2:$A$25,$A20)</f>
+        <f aca="false">COUNTIF('Pull Requests'!$A$2:$A$26,$A20)</f>
         <v>8</v>
       </c>
       <c r="C20" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A20,'Pull Requests'!$F$2:$F$25,"Merged")</f>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A20,'Pull Requests'!$F$2:$F$26,"Merged")</f>
         <v>8</v>
       </c>
       <c r="D20" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A20,'Pull Requests'!$F$2:$F$25,"Open - not merged")</f>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A20,'Pull Requests'!$F$2:$F$26,"Open - not merged")</f>
         <v>0</v>
       </c>
       <c r="E20" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A20,'Pull Requests'!$F$2:$F$25,"Draft - not merged")</f>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A20,'Pull Requests'!$F$2:$F$26,"Draft - not merged")</f>
         <v>0</v>
       </c>
     </row>
@@ -7466,20 +7448,20 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="n">
-        <f aca="false">COUNTIF('Pull Requests'!$A$2:$A$25,$A21)</f>
+        <f aca="false">COUNTIF('Pull Requests'!$A$2:$A$26,$A21)</f>
         <v>13</v>
       </c>
       <c r="C21" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A21,'Pull Requests'!$F$2:$F$25,"Merged")</f>
-        <v>11</v>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A21,'Pull Requests'!$F$2:$F$26,"Merged")</f>
+        <v>13</v>
       </c>
       <c r="D21" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A21,'Pull Requests'!$F$2:$F$25,"Open - not merged")</f>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A21,'Pull Requests'!$F$2:$F$26,"Open - not merged")</f>
         <v>0</v>
       </c>
       <c r="E21" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A21,'Pull Requests'!$F$2:$F$25,"Draft - not merged")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A21,'Pull Requests'!$F$2:$F$26,"Draft - not merged")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7487,19 +7469,19 @@
         <v>23</v>
       </c>
       <c r="B22" s="8" t="n">
-        <f aca="false">COUNTIF('Pull Requests'!$A$2:$A$25,$A22)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF('Pull Requests'!$A$2:$A$26,$A22)</f>
+        <v>4</v>
       </c>
       <c r="C22" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A22,'Pull Requests'!$F$2:$F$25,"Merged")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A22,'Pull Requests'!$F$2:$F$26,"Merged")</f>
+        <v>4</v>
       </c>
       <c r="D22" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A22,'Pull Requests'!$F$2:$F$25,"Open - not merged")</f>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A22,'Pull Requests'!$F$2:$F$26,"Open - not merged")</f>
         <v>0</v>
       </c>
       <c r="E22" s="8" t="n">
-        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$25,$A22,'Pull Requests'!$F$2:$F$25,"Draft - not merged")</f>
+        <f aca="false">COUNTIFS('Pull Requests'!$A$2:$A$26,$A22,'Pull Requests'!$F$2:$F$26,"Draft - not merged")</f>
         <v>0</v>
       </c>
     </row>
@@ -7509,11 +7491,11 @@
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">SUM(B20:B22)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9" t="n">
         <f aca="false">SUM(C20:C22)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D23" s="9" t="n">
         <f aca="false">SUM(D20:D22)</f>
@@ -7521,7 +7503,7 @@
       </c>
       <c r="E23" s="9" t="n">
         <f aca="false">SUM(E20:E22)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7577,7 +7559,7 @@
       </c>
       <c r="C28" s="8" t="n">
         <f aca="false">COUNTIFS(Branches!$A$2:$A$75,$A28,Branches!$H$2:$H$75,"Fully merged")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="8" t="n">
         <f aca="false">COUNTIFS(Branches!$A$2:$A$75,$A28,Branches!$H$2:$H$75,"Merged (same changes already in default)")</f>
@@ -7585,7 +7567,7 @@
       </c>
       <c r="E28" s="8" t="n">
         <f aca="false">COUNTIFS(Branches!$A$2:$A$75,$A28,Branches!$H$2:$H$75,"NOT merged")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7619,7 +7601,7 @@
       </c>
       <c r="C30" s="9" t="n">
         <f aca="false">SUM(C27:C29)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D30" s="9" t="n">
         <f aca="false">SUM(D27:D29)</f>
@@ -7627,7 +7609,7 @@
       </c>
       <c r="E30" s="9" t="n">
         <f aca="false">SUM(E27:E29)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25976,27 +25958,27 @@
       <c r="H366" s="5" t="s">
         <v>1544</v>
       </c>
-      <c r="I366" s="16" t="s">
-        <v>1345</v>
+      <c r="I366" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="J366" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="K366" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="L366" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M366" s="5" t="s">
         <v>1545</v>
-      </c>
-      <c r="K366" s="5" t="s">
-        <v>1546</v>
-      </c>
-      <c r="L366" s="16" t="s">
-        <v>1547</v>
-      </c>
-      <c r="M366" s="5" t="s">
-        <v>1548</v>
       </c>
       <c r="N366" s="5"/>
       <c r="O366" s="6" t="s">
-        <v>1549</v>
+        <v>1337</v>
       </c>
       <c r="P366" s="7" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26007,44 +25989,44 @@
         <v>1406</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="E367" s="6" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="F367" s="5" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
       <c r="G367" s="5" t="s">
         <v>1334</v>
       </c>
       <c r="H367" s="5" t="s">
-        <v>1555</v>
-      </c>
-      <c r="I367" s="16" t="s">
-        <v>1345</v>
+        <v>1551</v>
+      </c>
+      <c r="I367" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="J367" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="K367" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="L367" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M367" s="5" t="s">
         <v>1545</v>
-      </c>
-      <c r="K367" s="5" t="s">
-        <v>1556</v>
-      </c>
-      <c r="L367" s="16" t="s">
-        <v>1547</v>
-      </c>
-      <c r="M367" s="5" t="s">
-        <v>1557</v>
       </c>
       <c r="N367" s="5"/>
       <c r="O367" s="6" t="s">
-        <v>1558</v>
+        <v>1337</v>
       </c>
       <c r="P367" s="7" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26052,22 +26034,22 @@
         <v>23</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D368" s="6" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="F368" s="5" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="G368" s="5" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H368" s="5" t="s">
         <v>19</v>
@@ -26085,14 +26067,14 @@
         <v>82</v>
       </c>
       <c r="M368" s="5" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="N368" s="5"/>
       <c r="O368" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P368" s="7" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26100,22 +26082,22 @@
         <v>23</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="D369" s="6" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="E369" s="6" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F369" s="5" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="G369" s="5" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H369" s="5" t="s">
         <v>19</v>
@@ -26133,14 +26115,14 @@
         <v>82</v>
       </c>
       <c r="M369" s="5" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="N369" s="5"/>
       <c r="O369" s="6" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="P369" s="7" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26148,22 +26130,22 @@
         <v>23</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="D370" s="6" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="F370" s="5" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="G370" s="5" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H370" s="5" t="s">
         <v>19</v>
@@ -26181,14 +26163,14 @@
         <v>82</v>
       </c>
       <c r="M370" s="5" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="N370" s="5"/>
       <c r="O370" s="6" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="P370" s="7" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26196,22 +26178,22 @@
         <v>23</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="D371" s="6" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="E371" s="6" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="F371" s="5" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="G371" s="5" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H371" s="5" t="s">
         <v>19</v>
@@ -26229,14 +26211,14 @@
         <v>82</v>
       </c>
       <c r="M371" s="5" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="N371" s="5"/>
       <c r="O371" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P371" s="7" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26244,22 +26226,22 @@
         <v>23</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="D372" s="6" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="E372" s="6" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="F372" s="5" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="G372" s="5" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H372" s="5" t="s">
         <v>19</v>
@@ -26277,14 +26259,14 @@
         <v>82</v>
       </c>
       <c r="M372" s="5" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="N372" s="5"/>
       <c r="O372" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P372" s="7" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26292,22 +26274,22 @@
         <v>23</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="D373" s="6" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="E373" s="6" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="F373" s="5" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="G373" s="5" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H373" s="5" t="s">
         <v>19</v>
@@ -26325,14 +26307,14 @@
         <v>1348</v>
       </c>
       <c r="M373" s="5" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="N373" s="5"/>
       <c r="O373" s="6" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="P373" s="7" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26343,16 +26325,16 @@
         <v>247</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="D374" s="6" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="E374" s="6" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="F374" s="5" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="G374" s="5" t="s">
         <v>340</v>
@@ -26373,14 +26355,14 @@
         <v>82</v>
       </c>
       <c r="M374" s="5" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="N374" s="5"/>
       <c r="O374" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P374" s="7" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26391,16 +26373,16 @@
         <v>247</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
       <c r="D375" s="6" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="E375" s="6" t="s">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="F375" s="5" t="s">
-        <v>1604</v>
+        <v>1597</v>
       </c>
       <c r="G375" s="5" t="s">
         <v>340</v>
@@ -26421,14 +26403,14 @@
         <v>82</v>
       </c>
       <c r="M375" s="5" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="N375" s="5"/>
       <c r="O375" s="6" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="P375" s="7" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26439,16 +26421,16 @@
         <v>1339</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="D376" s="6" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
       <c r="E376" s="6" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="G376" s="5" t="s">
         <v>722</v>
@@ -26469,14 +26451,14 @@
         <v>82</v>
       </c>
       <c r="M376" s="5" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="N376" s="5"/>
       <c r="O376" s="6" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
       <c r="P376" s="7" t="s">
-        <v>1612</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26484,19 +26466,19 @@
         <v>23</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="D377" s="6" t="s">
-        <v>1615</v>
+        <v>1608</v>
       </c>
       <c r="E377" s="6" t="s">
-        <v>1616</v>
+        <v>1609</v>
       </c>
       <c r="F377" s="5" t="s">
-        <v>1617</v>
+        <v>1610</v>
       </c>
       <c r="G377" s="5" t="s">
         <v>1493</v>
@@ -26517,14 +26499,14 @@
         <v>82</v>
       </c>
       <c r="M377" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N377" s="5"/>
       <c r="O377" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P377" s="7" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26532,19 +26514,19 @@
         <v>23</v>
       </c>
       <c r="B378" s="5" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C378" s="5" t="s">
         <v>1613</v>
       </c>
-      <c r="C378" s="5" t="s">
-        <v>1620</v>
-      </c>
       <c r="D378" s="6" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
       <c r="E378" s="6" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
       <c r="F378" s="5" t="s">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="G378" s="5" t="s">
         <v>1506</v>
@@ -26565,14 +26547,14 @@
         <v>82</v>
       </c>
       <c r="M378" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N378" s="5"/>
       <c r="O378" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P378" s="7" t="s">
-        <v>1624</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26580,19 +26562,19 @@
         <v>23</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="D379" s="6" t="s">
-        <v>1626</v>
+        <v>1619</v>
       </c>
       <c r="E379" s="6" t="s">
-        <v>1627</v>
+        <v>1620</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="G379" s="5" t="s">
         <v>1506</v>
@@ -26613,14 +26595,14 @@
         <v>82</v>
       </c>
       <c r="M379" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N379" s="5"/>
       <c r="O379" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P379" s="7" t="s">
-        <v>1629</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26628,19 +26610,19 @@
         <v>23</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="D380" s="6" t="s">
-        <v>1631</v>
+        <v>1624</v>
       </c>
       <c r="E380" s="6" t="s">
-        <v>1632</v>
+        <v>1625</v>
       </c>
       <c r="F380" s="5" t="s">
-        <v>1633</v>
+        <v>1626</v>
       </c>
       <c r="G380" s="5" t="s">
         <v>1506</v>
@@ -26661,14 +26643,14 @@
         <v>82</v>
       </c>
       <c r="M380" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N380" s="5"/>
       <c r="O380" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P380" s="7" t="s">
-        <v>1634</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26676,19 +26658,19 @@
         <v>23</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>1635</v>
+        <v>1628</v>
       </c>
       <c r="D381" s="6" t="s">
-        <v>1636</v>
+        <v>1629</v>
       </c>
       <c r="E381" s="6" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
       <c r="F381" s="5" t="s">
-        <v>1638</v>
+        <v>1631</v>
       </c>
       <c r="G381" s="5" t="s">
         <v>1506</v>
@@ -26709,14 +26691,14 @@
         <v>82</v>
       </c>
       <c r="M381" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N381" s="5"/>
       <c r="O381" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P381" s="7" t="s">
-        <v>1639</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26724,22 +26706,22 @@
         <v>23</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="D382" s="6" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
       <c r="E382" s="6" t="s">
-        <v>1642</v>
+        <v>1635</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>1643</v>
+        <v>1636</v>
       </c>
       <c r="G382" s="5" t="s">
-        <v>1644</v>
+        <v>1637</v>
       </c>
       <c r="H382" s="5" t="s">
         <v>19</v>
@@ -26757,14 +26739,14 @@
         <v>82</v>
       </c>
       <c r="M382" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N382" s="5"/>
       <c r="O382" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P382" s="7" t="s">
-        <v>1645</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26772,22 +26754,22 @@
         <v>23</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>1646</v>
+        <v>1639</v>
       </c>
       <c r="D383" s="6" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="E383" s="6" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="G383" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H383" s="5" t="s">
         <v>19</v>
@@ -26805,14 +26787,14 @@
         <v>82</v>
       </c>
       <c r="M383" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N383" s="5"/>
       <c r="O383" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P383" s="7" t="s">
-        <v>1651</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26820,22 +26802,22 @@
         <v>23</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>1652</v>
+        <v>1645</v>
       </c>
       <c r="D384" s="6" t="s">
-        <v>1653</v>
+        <v>1646</v>
       </c>
       <c r="E384" s="6" t="s">
-        <v>1654</v>
+        <v>1647</v>
       </c>
       <c r="F384" s="5" t="s">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="G384" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H384" s="5" t="s">
         <v>19</v>
@@ -26853,14 +26835,14 @@
         <v>82</v>
       </c>
       <c r="M384" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N384" s="5"/>
       <c r="O384" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P384" s="7" t="s">
-        <v>1656</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26868,22 +26850,22 @@
         <v>23</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>1657</v>
+        <v>1650</v>
       </c>
       <c r="D385" s="6" t="s">
-        <v>1658</v>
+        <v>1651</v>
       </c>
       <c r="E385" s="6" t="s">
-        <v>1659</v>
+        <v>1652</v>
       </c>
       <c r="F385" s="5" t="s">
-        <v>1660</v>
+        <v>1653</v>
       </c>
       <c r="G385" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H385" s="5" t="s">
         <v>19</v>
@@ -26901,14 +26883,14 @@
         <v>82</v>
       </c>
       <c r="M385" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N385" s="5"/>
       <c r="O385" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P385" s="7" t="s">
-        <v>1661</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26916,22 +26898,22 @@
         <v>23</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>1662</v>
+        <v>1655</v>
       </c>
       <c r="D386" s="6" t="s">
-        <v>1663</v>
+        <v>1656</v>
       </c>
       <c r="E386" s="6" t="s">
-        <v>1664</v>
+        <v>1657</v>
       </c>
       <c r="F386" s="5" t="s">
-        <v>1665</v>
+        <v>1658</v>
       </c>
       <c r="G386" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H386" s="5" t="s">
         <v>19</v>
@@ -26949,14 +26931,14 @@
         <v>82</v>
       </c>
       <c r="M386" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N386" s="5"/>
       <c r="O386" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P386" s="7" t="s">
-        <v>1666</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26964,22 +26946,22 @@
         <v>23</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>1667</v>
+        <v>1660</v>
       </c>
       <c r="D387" s="6" t="s">
-        <v>1668</v>
+        <v>1661</v>
       </c>
       <c r="E387" s="6" t="s">
-        <v>1669</v>
+        <v>1662</v>
       </c>
       <c r="F387" s="5" t="s">
-        <v>1670</v>
+        <v>1663</v>
       </c>
       <c r="G387" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H387" s="5" t="s">
         <v>19</v>
@@ -26997,14 +26979,14 @@
         <v>82</v>
       </c>
       <c r="M387" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N387" s="5"/>
       <c r="O387" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P387" s="7" t="s">
-        <v>1671</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27012,22 +26994,22 @@
         <v>23</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>1672</v>
+        <v>1665</v>
       </c>
       <c r="D388" s="6" t="s">
-        <v>1673</v>
+        <v>1666</v>
       </c>
       <c r="E388" s="6" t="s">
-        <v>1674</v>
+        <v>1667</v>
       </c>
       <c r="F388" s="5" t="s">
-        <v>1675</v>
+        <v>1668</v>
       </c>
       <c r="G388" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H388" s="5" t="s">
         <v>19</v>
@@ -27045,14 +27027,14 @@
         <v>82</v>
       </c>
       <c r="M388" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N388" s="5"/>
       <c r="O388" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P388" s="7" t="s">
-        <v>1676</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27060,22 +27042,22 @@
         <v>23</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>1677</v>
+        <v>1670</v>
       </c>
       <c r="D389" s="6" t="s">
-        <v>1678</v>
+        <v>1671</v>
       </c>
       <c r="E389" s="6" t="s">
-        <v>1679</v>
+        <v>1672</v>
       </c>
       <c r="F389" s="5" t="s">
-        <v>1680</v>
+        <v>1673</v>
       </c>
       <c r="G389" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H389" s="5" t="s">
         <v>19</v>
@@ -27093,14 +27075,14 @@
         <v>82</v>
       </c>
       <c r="M389" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N389" s="5"/>
       <c r="O389" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P389" s="7" t="s">
-        <v>1681</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27108,22 +27090,22 @@
         <v>23</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>1682</v>
+        <v>1675</v>
       </c>
       <c r="D390" s="6" t="s">
-        <v>1683</v>
+        <v>1676</v>
       </c>
       <c r="E390" s="6" t="s">
-        <v>1684</v>
+        <v>1677</v>
       </c>
       <c r="F390" s="5" t="s">
-        <v>1685</v>
+        <v>1678</v>
       </c>
       <c r="G390" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H390" s="5" t="s">
         <v>19</v>
@@ -27141,14 +27123,14 @@
         <v>82</v>
       </c>
       <c r="M390" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N390" s="5"/>
       <c r="O390" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P390" s="7" t="s">
-        <v>1686</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27156,22 +27138,22 @@
         <v>23</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>1687</v>
+        <v>1680</v>
       </c>
       <c r="D391" s="6" t="s">
-        <v>1688</v>
+        <v>1681</v>
       </c>
       <c r="E391" s="6" t="s">
-        <v>1689</v>
+        <v>1682</v>
       </c>
       <c r="F391" s="5" t="s">
-        <v>1690</v>
+        <v>1683</v>
       </c>
       <c r="G391" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H391" s="5" t="s">
         <v>19</v>
@@ -27189,14 +27171,14 @@
         <v>82</v>
       </c>
       <c r="M391" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N391" s="5"/>
       <c r="O391" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P391" s="7" t="s">
-        <v>1691</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27204,22 +27186,22 @@
         <v>23</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>1692</v>
+        <v>1685</v>
       </c>
       <c r="D392" s="6" t="s">
-        <v>1693</v>
+        <v>1686</v>
       </c>
       <c r="E392" s="6" t="s">
-        <v>1694</v>
+        <v>1687</v>
       </c>
       <c r="F392" s="5" t="s">
-        <v>1695</v>
+        <v>1688</v>
       </c>
       <c r="G392" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H392" s="5" t="s">
         <v>19</v>
@@ -27237,14 +27219,14 @@
         <v>82</v>
       </c>
       <c r="M392" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N392" s="5"/>
       <c r="O392" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P392" s="7" t="s">
-        <v>1696</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27252,22 +27234,22 @@
         <v>23</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>1697</v>
+        <v>1690</v>
       </c>
       <c r="D393" s="6" t="s">
-        <v>1698</v>
+        <v>1691</v>
       </c>
       <c r="E393" s="6" t="s">
-        <v>1699</v>
+        <v>1692</v>
       </c>
       <c r="F393" s="5" t="s">
-        <v>1700</v>
+        <v>1693</v>
       </c>
       <c r="G393" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H393" s="5" t="s">
         <v>19</v>
@@ -27285,14 +27267,14 @@
         <v>82</v>
       </c>
       <c r="M393" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N393" s="5"/>
       <c r="O393" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P393" s="7" t="s">
-        <v>1701</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27300,22 +27282,22 @@
         <v>23</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>1702</v>
+        <v>1695</v>
       </c>
       <c r="D394" s="6" t="s">
-        <v>1703</v>
+        <v>1696</v>
       </c>
       <c r="E394" s="6" t="s">
-        <v>1704</v>
+        <v>1697</v>
       </c>
       <c r="F394" s="5" t="s">
-        <v>1705</v>
+        <v>1698</v>
       </c>
       <c r="G394" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H394" s="5" t="s">
         <v>19</v>
@@ -27333,14 +27315,14 @@
         <v>82</v>
       </c>
       <c r="M394" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N394" s="5"/>
       <c r="O394" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P394" s="7" t="s">
-        <v>1706</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27348,22 +27330,22 @@
         <v>23</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>1707</v>
+        <v>1700</v>
       </c>
       <c r="D395" s="6" t="s">
-        <v>1708</v>
+        <v>1701</v>
       </c>
       <c r="E395" s="6" t="s">
-        <v>1709</v>
+        <v>1702</v>
       </c>
       <c r="F395" s="5" t="s">
-        <v>1710</v>
+        <v>1703</v>
       </c>
       <c r="G395" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H395" s="5" t="s">
         <v>19</v>
@@ -27381,14 +27363,14 @@
         <v>82</v>
       </c>
       <c r="M395" s="5" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="N395" s="5"/>
       <c r="O395" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P395" s="7" t="s">
-        <v>1711</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27396,19 +27378,19 @@
         <v>23</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>1712</v>
+        <v>1705</v>
       </c>
       <c r="D396" s="6" t="s">
-        <v>1713</v>
+        <v>1706</v>
       </c>
       <c r="E396" s="6" t="s">
-        <v>1714</v>
+        <v>1707</v>
       </c>
       <c r="F396" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G396" s="5"/>
       <c r="H396" s="5" t="s">
@@ -27418,23 +27400,23 @@
         <v>1345</v>
       </c>
       <c r="J396" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K396" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L396" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M396" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N396" s="5"/>
       <c r="O396" s="6" t="s">
-        <v>1714</v>
+        <v>1707</v>
       </c>
       <c r="P396" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27442,19 +27424,19 @@
         <v>23</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="D397" s="6" t="s">
-        <v>1720</v>
+        <v>1713</v>
       </c>
       <c r="E397" s="6" t="s">
-        <v>1721</v>
+        <v>1714</v>
       </c>
       <c r="F397" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G397" s="5"/>
       <c r="H397" s="5" t="s">
@@ -27464,23 +27446,23 @@
         <v>1345</v>
       </c>
       <c r="J397" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K397" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L397" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M397" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N397" s="5"/>
       <c r="O397" s="6" t="s">
-        <v>1721</v>
+        <v>1714</v>
       </c>
       <c r="P397" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27488,19 +27470,19 @@
         <v>23</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>1722</v>
+        <v>1715</v>
       </c>
       <c r="D398" s="6" t="s">
-        <v>1723</v>
+        <v>1716</v>
       </c>
       <c r="E398" s="6" t="s">
-        <v>1724</v>
+        <v>1717</v>
       </c>
       <c r="F398" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G398" s="5"/>
       <c r="H398" s="5" t="s">
@@ -27510,23 +27492,23 @@
         <v>1345</v>
       </c>
       <c r="J398" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K398" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L398" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M398" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N398" s="5"/>
       <c r="O398" s="6" t="s">
-        <v>1724</v>
+        <v>1717</v>
       </c>
       <c r="P398" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27534,19 +27516,19 @@
         <v>23</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>1725</v>
+        <v>1718</v>
       </c>
       <c r="D399" s="6" t="s">
-        <v>1726</v>
+        <v>1719</v>
       </c>
       <c r="E399" s="6" t="s">
-        <v>1727</v>
+        <v>1720</v>
       </c>
       <c r="F399" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G399" s="5"/>
       <c r="H399" s="5" t="s">
@@ -27556,23 +27538,23 @@
         <v>1345</v>
       </c>
       <c r="J399" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K399" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L399" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M399" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N399" s="5"/>
       <c r="O399" s="6" t="s">
-        <v>1727</v>
+        <v>1720</v>
       </c>
       <c r="P399" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27580,19 +27562,19 @@
         <v>23</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>1728</v>
+        <v>1721</v>
       </c>
       <c r="D400" s="6" t="s">
-        <v>1729</v>
+        <v>1722</v>
       </c>
       <c r="E400" s="6" t="s">
-        <v>1730</v>
+        <v>1723</v>
       </c>
       <c r="F400" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G400" s="5"/>
       <c r="H400" s="5" t="s">
@@ -27602,23 +27584,23 @@
         <v>1345</v>
       </c>
       <c r="J400" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K400" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L400" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M400" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N400" s="5"/>
       <c r="O400" s="6" t="s">
-        <v>1730</v>
+        <v>1723</v>
       </c>
       <c r="P400" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27626,19 +27608,19 @@
         <v>23</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>1731</v>
+        <v>1724</v>
       </c>
       <c r="D401" s="6" t="s">
-        <v>1732</v>
+        <v>1725</v>
       </c>
       <c r="E401" s="6" t="s">
-        <v>1733</v>
+        <v>1726</v>
       </c>
       <c r="F401" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G401" s="5"/>
       <c r="H401" s="5" t="s">
@@ -27648,23 +27630,23 @@
         <v>1345</v>
       </c>
       <c r="J401" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K401" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L401" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M401" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N401" s="5"/>
       <c r="O401" s="6" t="s">
-        <v>1733</v>
+        <v>1726</v>
       </c>
       <c r="P401" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27672,19 +27654,19 @@
         <v>23</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>1734</v>
+        <v>1727</v>
       </c>
       <c r="D402" s="6" t="s">
-        <v>1735</v>
+        <v>1728</v>
       </c>
       <c r="E402" s="6" t="s">
-        <v>1736</v>
+        <v>1729</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G402" s="5"/>
       <c r="H402" s="5" t="s">
@@ -27694,23 +27676,23 @@
         <v>1345</v>
       </c>
       <c r="J402" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K402" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L402" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M402" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N402" s="5"/>
       <c r="O402" s="6" t="s">
-        <v>1736</v>
+        <v>1729</v>
       </c>
       <c r="P402" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27718,19 +27700,19 @@
         <v>23</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
       <c r="D403" s="6" t="s">
-        <v>1738</v>
+        <v>1731</v>
       </c>
       <c r="E403" s="6" t="s">
-        <v>1739</v>
+        <v>1732</v>
       </c>
       <c r="F403" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G403" s="5"/>
       <c r="H403" s="5" t="s">
@@ -27740,23 +27722,23 @@
         <v>1345</v>
       </c>
       <c r="J403" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K403" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L403" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M403" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N403" s="5"/>
       <c r="O403" s="6" t="s">
-        <v>1739</v>
+        <v>1732</v>
       </c>
       <c r="P403" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27764,19 +27746,19 @@
         <v>23</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>1740</v>
+        <v>1733</v>
       </c>
       <c r="D404" s="6" t="s">
-        <v>1741</v>
+        <v>1734</v>
       </c>
       <c r="E404" s="6" t="s">
-        <v>1742</v>
+        <v>1735</v>
       </c>
       <c r="F404" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G404" s="5"/>
       <c r="H404" s="5" t="s">
@@ -27786,23 +27768,23 @@
         <v>1345</v>
       </c>
       <c r="J404" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K404" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L404" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M404" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N404" s="5"/>
       <c r="O404" s="6" t="s">
-        <v>1742</v>
+        <v>1735</v>
       </c>
       <c r="P404" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27810,19 +27792,19 @@
         <v>23</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>1743</v>
+        <v>1736</v>
       </c>
       <c r="D405" s="6" t="s">
-        <v>1744</v>
+        <v>1737</v>
       </c>
       <c r="E405" s="6" t="s">
-        <v>1745</v>
+        <v>1738</v>
       </c>
       <c r="F405" s="5" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="G405" s="5"/>
       <c r="H405" s="5" t="s">
@@ -27832,23 +27814,23 @@
         <v>1345</v>
       </c>
       <c r="J405" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="K405" s="5" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="L405" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="M405" s="5" t="s">
         <v>272</v>
       </c>
       <c r="N405" s="5"/>
       <c r="O405" s="6" t="s">
-        <v>1745</v>
+        <v>1738</v>
       </c>
       <c r="P405" s="7" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27856,19 +27838,19 @@
         <v>23</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>1746</v>
+        <v>1739</v>
       </c>
       <c r="D406" s="6" t="s">
-        <v>1747</v>
+        <v>1740</v>
       </c>
       <c r="E406" s="6" t="s">
-        <v>1748</v>
+        <v>1741</v>
       </c>
       <c r="F406" s="5" t="s">
-        <v>1749</v>
+        <v>1742</v>
       </c>
       <c r="G406" s="5" t="s">
         <v>1334</v>
@@ -27889,14 +27871,14 @@
         <v>82</v>
       </c>
       <c r="M406" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N406" s="5"/>
       <c r="O406" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P406" s="7" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27904,19 +27886,19 @@
         <v>23</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>1752</v>
+        <v>1745</v>
       </c>
       <c r="D407" s="6" t="s">
-        <v>1753</v>
+        <v>1746</v>
       </c>
       <c r="E407" s="6" t="s">
-        <v>1754</v>
+        <v>1747</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>1749</v>
+        <v>1742</v>
       </c>
       <c r="G407" s="5" t="s">
         <v>1334</v>
@@ -27937,14 +27919,14 @@
         <v>82</v>
       </c>
       <c r="M407" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N407" s="5"/>
       <c r="O407" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P407" s="7" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27952,19 +27934,19 @@
         <v>23</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>1755</v>
+        <v>1748</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>1756</v>
+        <v>1749</v>
       </c>
       <c r="E408" s="6" t="s">
-        <v>1757</v>
+        <v>1750</v>
       </c>
       <c r="F408" s="5" t="s">
-        <v>1749</v>
+        <v>1742</v>
       </c>
       <c r="G408" s="5" t="s">
         <v>1334</v>
@@ -27985,14 +27967,14 @@
         <v>82</v>
       </c>
       <c r="M408" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N408" s="5"/>
       <c r="O408" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P408" s="7" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28003,16 +27985,16 @@
         <v>247</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>1758</v>
+        <v>1751</v>
       </c>
       <c r="D409" s="6" t="s">
-        <v>1759</v>
+        <v>1752</v>
       </c>
       <c r="E409" s="6" t="s">
-        <v>1760</v>
+        <v>1753</v>
       </c>
       <c r="F409" s="5" t="s">
-        <v>1749</v>
+        <v>1742</v>
       </c>
       <c r="G409" s="5" t="s">
         <v>1334</v>
@@ -28033,14 +28015,14 @@
         <v>82</v>
       </c>
       <c r="M409" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N409" s="5"/>
       <c r="O409" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P409" s="7" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28048,19 +28030,19 @@
         <v>23</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>1761</v>
+        <v>1754</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>1762</v>
+        <v>1755</v>
       </c>
       <c r="E410" s="6" t="s">
-        <v>1763</v>
+        <v>1756</v>
       </c>
       <c r="F410" s="5" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
       <c r="G410" s="5" t="s">
         <v>1334</v>
@@ -28081,14 +28063,14 @@
         <v>82</v>
       </c>
       <c r="M410" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N410" s="5"/>
       <c r="O410" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P410" s="7" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28096,19 +28078,19 @@
         <v>23</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>1766</v>
+        <v>1759</v>
       </c>
       <c r="D411" s="6" t="s">
-        <v>1767</v>
+        <v>1760</v>
       </c>
       <c r="E411" s="6" t="s">
-        <v>1768</v>
+        <v>1761</v>
       </c>
       <c r="F411" s="5" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
       <c r="G411" s="5" t="s">
         <v>1334</v>
@@ -28129,14 +28111,14 @@
         <v>82</v>
       </c>
       <c r="M411" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N411" s="5"/>
       <c r="O411" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P411" s="7" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28147,16 +28129,16 @@
         <v>1527</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>1769</v>
+        <v>1762</v>
       </c>
       <c r="D412" s="6" t="s">
-        <v>1770</v>
+        <v>1763</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>1771</v>
+        <v>1764</v>
       </c>
       <c r="F412" s="5" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
       <c r="G412" s="5" t="s">
         <v>1334</v>
@@ -28177,14 +28159,14 @@
         <v>82</v>
       </c>
       <c r="M412" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N412" s="5"/>
       <c r="O412" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P412" s="7" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28195,16 +28177,16 @@
         <v>1539</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>1772</v>
+        <v>1765</v>
       </c>
       <c r="D413" s="6" t="s">
-        <v>1773</v>
+        <v>1766</v>
       </c>
       <c r="E413" s="6" t="s">
-        <v>1774</v>
+        <v>1767</v>
       </c>
       <c r="F413" s="5" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
       <c r="G413" s="5" t="s">
         <v>1334</v>
@@ -28225,14 +28207,14 @@
         <v>82</v>
       </c>
       <c r="M413" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N413" s="5"/>
       <c r="O413" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P413" s="7" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28240,19 +28222,19 @@
         <v>23</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="D414" s="6" t="s">
-        <v>1776</v>
+        <v>1769</v>
       </c>
       <c r="E414" s="6" t="s">
-        <v>1777</v>
+        <v>1770</v>
       </c>
       <c r="F414" s="5" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
       <c r="G414" s="5" t="s">
         <v>1334</v>
@@ -28273,14 +28255,14 @@
         <v>82</v>
       </c>
       <c r="M414" s="5" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="N414" s="5"/>
       <c r="O414" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P414" s="7" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28291,16 +28273,16 @@
         <v>1339</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>1778</v>
+        <v>1771</v>
       </c>
       <c r="D415" s="6" t="s">
-        <v>1779</v>
+        <v>1772</v>
       </c>
       <c r="E415" s="6" t="s">
-        <v>1780</v>
+        <v>1773</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>1781</v>
+        <v>1774</v>
       </c>
       <c r="G415" s="5" t="s">
         <v>1334</v>
@@ -28321,14 +28303,14 @@
         <v>82</v>
       </c>
       <c r="M415" s="5" t="s">
-        <v>1782</v>
+        <v>1775</v>
       </c>
       <c r="N415" s="5"/>
       <c r="O415" s="6" t="s">
         <v>1337</v>
       </c>
       <c r="P415" s="7" t="s">
-        <v>1783</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28339,44 +28321,44 @@
         <v>247</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>1784</v>
+        <v>1777</v>
       </c>
       <c r="D416" s="6" t="s">
-        <v>1785</v>
+        <v>1778</v>
       </c>
       <c r="E416" s="6" t="s">
-        <v>1786</v>
+        <v>1779</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1787</v>
+        <v>1780</v>
       </c>
       <c r="G416" s="5" t="s">
-        <v>1334</v>
+        <v>14</v>
       </c>
       <c r="H416" s="5" t="s">
-        <v>1544</v>
-      </c>
-      <c r="I416" s="16" t="s">
-        <v>1345</v>
+        <v>19</v>
+      </c>
+      <c r="I416" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="J416" s="5" t="s">
-        <v>1545</v>
+        <v>1366</v>
       </c>
       <c r="K416" s="5" t="s">
-        <v>1546</v>
-      </c>
-      <c r="L416" s="16" t="s">
-        <v>1547</v>
+        <v>1367</v>
+      </c>
+      <c r="L416" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="M416" s="5" t="s">
-        <v>1788</v>
+        <v>1781</v>
       </c>
       <c r="N416" s="5"/>
       <c r="O416" s="6" t="s">
-        <v>1789</v>
+        <v>1782</v>
       </c>
       <c r="P416" s="7" t="s">
-        <v>1790</v>
+        <v>1783</v>
       </c>
     </row>
   </sheetData>
@@ -28802,7 +28784,7 @@
     <hyperlink ref="P413" r:id="rId412" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/2"/>
     <hyperlink ref="P414" r:id="rId413" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/2"/>
     <hyperlink ref="P415" r:id="rId414" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/3"/>
-    <hyperlink ref="P416" r:id="rId415" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pulls"/>
+    <hyperlink ref="P416" r:id="rId415" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/4"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -28834,36 +28816,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>1791</v>
+        <v>1784</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1792</v>
+        <v>1785</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1794</v>
+        <v>1787</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1795</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>1796</v>
+        <v>1789</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1797</v>
+        <v>1790</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1798</v>
+        <v>1791</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>79</v>
@@ -28875,18 +28857,18 @@
         <v>82</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>1800</v>
+        <v>1793</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1801</v>
+        <v>1794</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1802</v>
+        <v>1795</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>79</v>
@@ -28898,18 +28880,18 @@
         <v>82</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>1803</v>
+        <v>1796</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1804</v>
+        <v>1797</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1805</v>
+        <v>1798</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>79</v>
@@ -28918,21 +28900,21 @@
         <v>259</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>1807</v>
+        <v>1800</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1808</v>
+        <v>1801</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1809</v>
+        <v>1802</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>79</v>
@@ -28941,21 +28923,21 @@
         <v>259</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>1810</v>
+        <v>1803</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1811</v>
+        <v>1804</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1812</v>
+        <v>1805</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>79</v>
@@ -28964,21 +28946,21 @@
         <v>259</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1813</v>
+        <v>1806</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1814</v>
+        <v>1807</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1815</v>
+        <v>1808</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>79</v>
@@ -28987,21 +28969,21 @@
         <v>259</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>1816</v>
+        <v>1809</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1817</v>
+        <v>1810</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1818</v>
+        <v>1811</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>79</v>
@@ -29010,21 +28992,21 @@
         <v>259</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1819</v>
+        <v>1812</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>1820</v>
+        <v>1813</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1821</v>
+        <v>1814</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1822</v>
+        <v>1815</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>79</v>
@@ -29033,21 +29015,21 @@
         <v>1074</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1823</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>1824</v>
+        <v>1817</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1825</v>
+        <v>1818</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1826</v>
+        <v>1819</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>79</v>
@@ -29056,21 +29038,21 @@
         <v>1074</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>1827</v>
+        <v>1820</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1828</v>
+        <v>1821</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1829</v>
+        <v>1822</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>79</v>
@@ -29079,21 +29061,21 @@
         <v>1074</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>1830</v>
+        <v>1823</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1831</v>
+        <v>1824</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1832</v>
+        <v>1825</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>79</v>
@@ -29102,21 +29084,21 @@
         <v>1074</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>1833</v>
+        <v>1826</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>79</v>
@@ -29125,21 +29107,21 @@
         <v>1074</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>1836</v>
+        <v>1829</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1837</v>
+        <v>1830</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1838</v>
+        <v>1831</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>79</v>
@@ -29148,21 +29130,21 @@
         <v>1074</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>1839</v>
+        <v>1832</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1840</v>
+        <v>1833</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1841</v>
+        <v>1834</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>79</v>
@@ -29171,21 +29153,21 @@
         <v>1074</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>1842</v>
+        <v>1835</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1843</v>
+        <v>1836</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1844</v>
+        <v>1837</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>79</v>
@@ -29194,21 +29176,21 @@
         <v>1074</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>1845</v>
+        <v>1838</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1847</v>
+        <v>1840</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>79</v>
@@ -29217,21 +29199,21 @@
         <v>1074</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>1848</v>
+        <v>1841</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1849</v>
+        <v>1842</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1850</v>
+        <v>1843</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>79</v>
@@ -29240,21 +29222,21 @@
         <v>1074</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>1851</v>
+        <v>1844</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1852</v>
+        <v>1845</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1853</v>
+        <v>1846</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>79</v>
@@ -29263,21 +29245,21 @@
         <v>1074</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1854</v>
+        <v>1847</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>1855</v>
+        <v>1848</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1856</v>
+        <v>1849</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1857</v>
+        <v>1850</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>79</v>
@@ -29286,21 +29268,21 @@
         <v>1074</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1858</v>
+        <v>1851</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>1859</v>
+        <v>1852</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1860</v>
+        <v>1853</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1861</v>
+        <v>1854</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>79</v>
@@ -29309,21 +29291,21 @@
         <v>1074</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>1862</v>
+        <v>1855</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1863</v>
+        <v>1856</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1864</v>
+        <v>1857</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>79</v>
@@ -29332,21 +29314,21 @@
         <v>398</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>1865</v>
+        <v>1858</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1866</v>
+        <v>1859</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1867</v>
+        <v>1860</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>79</v>
@@ -29355,21 +29337,21 @@
         <v>398</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>1868</v>
+        <v>1861</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1869</v>
+        <v>1862</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1870</v>
+        <v>1863</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>79</v>
@@ -29378,21 +29360,21 @@
         <v>735</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>1871</v>
+        <v>1864</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1872</v>
+        <v>1865</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1873</v>
+        <v>1866</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>79</v>
@@ -29401,21 +29383,21 @@
         <v>735</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>1874</v>
+        <v>1867</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1875</v>
+        <v>1868</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1876</v>
+        <v>1869</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>79</v>
@@ -29424,21 +29406,21 @@
         <v>735</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>1878</v>
+        <v>1871</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1879</v>
+        <v>1872</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1880</v>
+        <v>1873</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>79</v>
@@ -29447,21 +29429,21 @@
         <v>722</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>1881</v>
+        <v>1874</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1882</v>
+        <v>1875</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1883</v>
+        <v>1876</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>79</v>
@@ -29470,21 +29452,21 @@
         <v>722</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>1884</v>
+        <v>1877</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1885</v>
+        <v>1878</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1886</v>
+        <v>1879</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>79</v>
@@ -29493,21 +29475,21 @@
         <v>722</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>1887</v>
+        <v>1880</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1888</v>
+        <v>1881</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>79</v>
@@ -29516,21 +29498,21 @@
         <v>722</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>1890</v>
+        <v>1883</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1891</v>
+        <v>1884</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1892</v>
+        <v>1885</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>79</v>
@@ -29539,21 +29521,21 @@
         <v>722</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>1893</v>
+        <v>1886</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1894</v>
+        <v>1887</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>1895</v>
+        <v>1888</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>79</v>
@@ -29562,21 +29544,21 @@
         <v>722</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>1896</v>
+        <v>1889</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>79</v>
@@ -29585,21 +29567,21 @@
         <v>722</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1900</v>
+        <v>1893</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>1901</v>
+        <v>1894</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>79</v>
@@ -29608,18 +29590,18 @@
         <v>722</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>1902</v>
+        <v>1895</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1903</v>
+        <v>1896</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>1344</v>
@@ -29631,21 +29613,21 @@
         <v>722</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>1904</v>
+        <v>1897</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>1905</v>
+        <v>1898</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1906</v>
+        <v>1899</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>1907</v>
+        <v>1900</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>79</v>
@@ -29654,21 +29636,21 @@
         <v>722</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>1908</v>
+        <v>1901</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1909</v>
+        <v>1902</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>79</v>
@@ -29677,21 +29659,21 @@
         <v>722</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>1911</v>
+        <v>1904</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>1913</v>
+        <v>1906</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>79</v>
@@ -29700,21 +29682,21 @@
         <v>722</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1915</v>
+        <v>1908</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>1916</v>
+        <v>1909</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>79</v>
@@ -29723,21 +29705,21 @@
         <v>722</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>1917</v>
+        <v>1910</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>1918</v>
+        <v>1911</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>1919</v>
+        <v>1912</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>79</v>
@@ -29746,21 +29728,21 @@
         <v>722</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>1920</v>
+        <v>1913</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1921</v>
+        <v>1914</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>1922</v>
+        <v>1915</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>79</v>
@@ -29769,21 +29751,21 @@
         <v>1334</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>1923</v>
+        <v>1916</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>1924</v>
+        <v>1917</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>1925</v>
+        <v>1918</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>79</v>
@@ -29792,18 +29774,18 @@
         <v>1334</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>1926</v>
+        <v>1919</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>1927</v>
+        <v>1920</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>1335</v>
@@ -29815,44 +29797,44 @@
         <v>1334</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>1928</v>
+        <v>1921</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>1929</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>1930</v>
+        <v>1923</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>1931</v>
+        <v>1924</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>1932</v>
+        <v>1925</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>1928</v>
+        <v>1921</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>1929</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>1934</v>
+        <v>1927</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>1935</v>
+        <v>1928</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>1936</v>
+        <v>1929</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>79</v>
@@ -29861,18 +29843,18 @@
         <v>1334</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>1928</v>
+        <v>1921</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>1937</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>1938</v>
+        <v>1931</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>1939</v>
+        <v>1932</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>1335</v>
@@ -29884,15 +29866,15 @@
         <v>14</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>1940</v>
+        <v>1933</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>1941</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>1942</v>
+        <v>1935</v>
       </c>
     </row>
   </sheetData>
@@ -29913,7 +29895,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -29932,28 +29914,28 @@
         <v>3</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>1943</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1944</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1945</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1946</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1947</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>1948</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1949</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1950</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>72</v>
@@ -29967,7 +29949,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1951</v>
+        <v>1944</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1335</v>
@@ -29999,10 +29981,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1952</v>
+        <v>1945</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1936</v>
+        <v>1929</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>12</v>
@@ -30020,7 +30002,7 @@
         <v>79</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>1953</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30031,7 +30013,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1954</v>
+        <v>1947</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>1335</v>
@@ -30052,7 +30034,7 @@
         <v>79</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>1955</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30063,10 +30045,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1956</v>
+        <v>1949</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1925</v>
+        <v>1918</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>12</v>
@@ -30084,7 +30066,7 @@
         <v>79</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>1957</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30095,10 +30077,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1958</v>
+        <v>1951</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1922</v>
+        <v>1915</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>12</v>
@@ -30116,7 +30098,7 @@
         <v>79</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>1959</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30127,7 +30109,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1960</v>
+        <v>1953</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>1335</v>
@@ -30139,7 +30121,7 @@
         <v>44</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>104</v>
@@ -30148,7 +30130,7 @@
         <v>79</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>1961</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30159,10 +30141,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1962</v>
+        <v>1955</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1932</v>
+        <v>1925</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>12</v>
@@ -30171,16 +30153,16 @@
         <v>44</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>79</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>1963</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30191,7 +30173,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1964</v>
+        <v>1957</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>1335</v>
@@ -30206,13 +30188,13 @@
         <v>722</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>79</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>1965</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30223,28 +30205,28 @@
         <v>12</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1966</v>
+        <v>1959</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>46</v>
+      <c r="F10" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>1334</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>1337</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>1345</v>
+        <v>14</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30255,7 +30237,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1967</v>
+        <v>1960</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>1544</v>
@@ -30263,20 +30245,20 @@
       <c r="E11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>46</v>
+      <c r="F11" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>1334</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1337</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>1345</v>
+        <v>14</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30287,10 +30269,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1968</v>
+        <v>1961</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>19</v>
@@ -30319,7 +30301,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1969</v>
+        <v>1962</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>1335</v>
@@ -30351,7 +30333,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1970</v>
+        <v>1963</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>1524</v>
@@ -30383,10 +30365,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1971</v>
+        <v>1964</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>19</v>
@@ -30415,10 +30397,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1972</v>
+        <v>1965</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>19</v>
@@ -30447,10 +30429,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1974</v>
+        <v>1967</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>19</v>
@@ -30479,10 +30461,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1975</v>
+        <v>1968</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1976</v>
+        <v>1969</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>19</v>
@@ -30511,10 +30493,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1977</v>
+        <v>1970</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1978</v>
+        <v>1971</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>19</v>
@@ -30543,10 +30525,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1979</v>
+        <v>1972</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1980</v>
+        <v>1973</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>19</v>
@@ -30564,7 +30546,7 @@
         <v>79</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>1981</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30575,10 +30557,10 @@
         <v>2</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1982</v>
+        <v>1975</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1983</v>
+        <v>1976</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>19</v>
@@ -30607,10 +30589,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1984</v>
+        <v>1977</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1985</v>
+        <v>1978</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>19</v>
@@ -30628,7 +30610,7 @@
         <v>79</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>1986</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30636,10 +30618,10 @@
         <v>23</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1987</v>
+        <v>1980</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>1544</v>
@@ -30654,7 +30636,7 @@
         <v>1334</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>1334</v>
+        <v>14</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>79</v>
@@ -30663,18 +30645,18 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1988</v>
+        <v>1981</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1524</v>
+        <v>1544</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>19</v>
@@ -30683,7 +30665,7 @@
         <v>44</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>1933</v>
+        <v>1334</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>1334</v>
@@ -30692,21 +30674,21 @@
         <v>79</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1989</v>
+        <v>1982</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1335</v>
+        <v>1524</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>19</v>
@@ -30715,7 +30697,7 @@
         <v>44</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>722</v>
+        <v>1926</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>1334</v>
@@ -30724,11 +30706,43 @@
         <v>79</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>1751</v>
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>1744</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J25"/>
+  <autoFilter ref="A1:J26"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" display="https://github.com/sanjaymorankar-debug/ATIP-DEV/pull/8"/>
     <hyperlink ref="J3" r:id="rId2" display="https://github.com/sanjaymorankar-debug/ATIP-DEV/pull/7"/>
@@ -30751,9 +30765,10 @@
     <hyperlink ref="J20" r:id="rId19" display="https://github.com/sanjaymorankar-debug/bkesari/pull/3"/>
     <hyperlink ref="J21" r:id="rId20" display="https://github.com/sanjaymorankar-debug/bkesari/pull/2"/>
     <hyperlink ref="J22" r:id="rId21" display="https://github.com/sanjaymorankar-debug/bkesari/pull/1"/>
-    <hyperlink ref="J23" r:id="rId22" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/3"/>
-    <hyperlink ref="J24" r:id="rId23" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/2"/>
-    <hyperlink ref="J25" r:id="rId24" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/1"/>
+    <hyperlink ref="J23" r:id="rId22" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/4"/>
+    <hyperlink ref="J24" r:id="rId23" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/3"/>
+    <hyperlink ref="J25" r:id="rId24" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/2"/>
+    <hyperlink ref="J26" r:id="rId25" display="https://github.com/sanjaymorankar-debug/bkesari-platform/pull/1"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30762,7 +30777,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId25"/>
+  <drawing r:id="rId26"/>
 </worksheet>
 </file>
 
@@ -30791,25 +30806,25 @@
         <v>64</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1986</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>1987</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1989</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>1990</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1992</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1993</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>1994</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1995</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1996</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30817,13 +30832,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1997</v>
+        <v>1991</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1998</v>
+        <v>1992</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -30838,7 +30853,7 @@
         <v>49</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30846,13 +30861,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>735</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -30867,7 +30882,7 @@
         <v>49</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30875,13 +30890,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>2002</v>
+        <v>1996</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
@@ -30896,7 +30911,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30904,13 +30919,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -30925,7 +30940,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30933,13 +30948,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -30954,7 +30969,7 @@
         <v>49</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30962,13 +30977,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -30983,7 +30998,7 @@
         <v>49</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30991,13 +31006,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0</v>
@@ -31012,7 +31027,7 @@
         <v>49</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31020,13 +31035,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -31041,7 +31056,7 @@
         <v>49</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31049,13 +31064,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0</v>
@@ -31070,7 +31085,7 @@
         <v>49</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31078,13 +31093,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -31099,7 +31114,7 @@
         <v>49</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31107,13 +31122,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
@@ -31128,7 +31143,7 @@
         <v>49</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31136,13 +31151,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -31157,7 +31172,7 @@
         <v>49</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31165,13 +31180,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>0</v>
@@ -31186,7 +31201,7 @@
         <v>49</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31194,13 +31209,13 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1922</v>
+        <v>1915</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -31215,7 +31230,7 @@
         <v>49</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31223,13 +31238,13 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1936</v>
+        <v>1929</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>104</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1952</v>
+        <v>1945</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>0</v>
@@ -31244,7 +31259,7 @@
         <v>49</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>2026</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31258,7 +31273,7 @@
         <v>1334</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -31273,7 +31288,7 @@
         <v>49</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>2028</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31281,13 +31296,13 @@
         <v>10</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1932</v>
+        <v>1925</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>2029</v>
+        <v>2023</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
@@ -31302,7 +31317,7 @@
         <v>49</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>2030</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31310,13 +31325,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1925</v>
+        <v>1918</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>1334</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>2031</v>
+        <v>2025</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -31331,7 +31346,7 @@
         <v>49</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>2032</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31339,13 +31354,13 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>2033</v>
+        <v>2027</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2034</v>
+        <v>2028</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>1</v>
@@ -31357,7 +31372,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="I20" s="6"/>
     </row>
@@ -31366,13 +31381,13 @@
         <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>2036</v>
+        <v>2030</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -31420,13 +31435,13 @@
         <v>10</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>2037</v>
+        <v>2031</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>735</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2038</v>
+        <v>2032</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -31447,13 +31462,13 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1798</v>
+        <v>1791</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2039</v>
+        <v>2033</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0</v>
@@ -31474,13 +31489,13 @@
         <v>10</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1829</v>
+        <v>1822</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>2040</v>
+        <v>2034</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0</v>
@@ -31501,13 +31516,13 @@
         <v>10</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1832</v>
+        <v>1825</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>2041</v>
+        <v>2035</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0</v>
@@ -31528,13 +31543,13 @@
         <v>10</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>2042</v>
+        <v>2036</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0</v>
@@ -31555,13 +31570,13 @@
         <v>10</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1838</v>
+        <v>1831</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>2043</v>
+        <v>2037</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>0</v>
@@ -31582,13 +31597,13 @@
         <v>10</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>1844</v>
+        <v>1837</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0</v>
@@ -31609,13 +31624,13 @@
         <v>10</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1841</v>
+        <v>1834</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>2045</v>
+        <v>2039</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>0</v>
@@ -31636,13 +31651,13 @@
         <v>10</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>1847</v>
+        <v>1840</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>2046</v>
+        <v>2040</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>0</v>
@@ -31663,13 +31678,13 @@
         <v>10</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>1850</v>
+        <v>1843</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>0</v>
@@ -31690,13 +31705,13 @@
         <v>10</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>1853</v>
+        <v>1846</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>2048</v>
+        <v>2042</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>0</v>
@@ -31717,13 +31732,13 @@
         <v>10</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>1857</v>
+        <v>1850</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>2049</v>
+        <v>2043</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>0</v>
@@ -31744,13 +31759,13 @@
         <v>10</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>1802</v>
+        <v>1795</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0</v>
@@ -31771,13 +31786,13 @@
         <v>10</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>1861</v>
+        <v>1854</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>2050</v>
+        <v>2044</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>0</v>
@@ -31798,13 +31813,13 @@
         <v>10</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>1864</v>
+        <v>1857</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>398</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>2051</v>
+        <v>2045</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0</v>
@@ -31825,13 +31840,13 @@
         <v>10</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>1867</v>
+        <v>1860</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>398</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>2052</v>
+        <v>2046</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>0</v>
@@ -31852,13 +31867,13 @@
         <v>10</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1870</v>
+        <v>1863</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>735</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>2053</v>
+        <v>2047</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>0</v>
@@ -31879,13 +31894,13 @@
         <v>10</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>1873</v>
+        <v>1866</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>735</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>0</v>
@@ -31906,13 +31921,13 @@
         <v>10</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>1876</v>
+        <v>1869</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>735</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>0</v>
@@ -31933,13 +31948,13 @@
         <v>10</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>1880</v>
+        <v>1873</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>735</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>2055</v>
+        <v>2049</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
@@ -31960,13 +31975,13 @@
         <v>10</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>1883</v>
+        <v>1876</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>0</v>
@@ -31993,7 +32008,7 @@
         <v>340</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>1</v>
@@ -32008,7 +32023,7 @@
         <v>51</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>2058</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32016,13 +32031,13 @@
         <v>10</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>1886</v>
+        <v>1879</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>2059</v>
+        <v>2053</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
@@ -32043,13 +32058,13 @@
         <v>10</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>2060</v>
+        <v>2054</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0</v>
@@ -32070,13 +32085,13 @@
         <v>10</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>1892</v>
+        <v>1885</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>2061</v>
+        <v>2055</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0</v>
@@ -32097,13 +32112,13 @@
         <v>10</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>1805</v>
+        <v>1798</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0</v>
@@ -32124,13 +32139,13 @@
         <v>10</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>1895</v>
+        <v>1888</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>2062</v>
+        <v>2056</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
@@ -32151,13 +32166,13 @@
         <v>10</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>2063</v>
+        <v>2057</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
@@ -32178,13 +32193,13 @@
         <v>10</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>1901</v>
+        <v>1894</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>2064</v>
+        <v>2058</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
@@ -32211,7 +32226,7 @@
         <v>722</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>2065</v>
+        <v>2059</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>1</v>
@@ -32226,7 +32241,7 @@
         <v>51</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>2066</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32234,13 +32249,13 @@
         <v>10</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>1907</v>
+        <v>1900</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
@@ -32261,13 +32276,13 @@
         <v>10</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>2068</v>
+        <v>2062</v>
       </c>
       <c r="E54" s="5" t="n">
         <v>0</v>
@@ -32288,13 +32303,13 @@
         <v>10</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>1913</v>
+        <v>1906</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>2069</v>
+        <v>2063</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
@@ -32315,13 +32330,13 @@
         <v>10</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>1916</v>
+        <v>1909</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>2070</v>
+        <v>2064</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0</v>
@@ -32342,13 +32357,13 @@
         <v>10</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>1919</v>
+        <v>1912</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
@@ -32369,13 +32384,13 @@
         <v>10</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>2072</v>
+        <v>2066</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>2073</v>
+        <v>2067</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>0</v>
@@ -32396,13 +32411,13 @@
         <v>10</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1809</v>
+        <v>1802</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
@@ -32423,13 +32438,13 @@
         <v>10</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>1812</v>
+        <v>1805</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>0</v>
@@ -32450,13 +32465,13 @@
         <v>10</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>1815</v>
+        <v>1808</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
@@ -32477,13 +32492,13 @@
         <v>10</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>1818</v>
+        <v>1811</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
@@ -32504,13 +32519,13 @@
         <v>10</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>1822</v>
+        <v>1815</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
@@ -32531,13 +32546,13 @@
         <v>10</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>0</v>
@@ -32558,13 +32573,13 @@
         <v>10</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>1826</v>
+        <v>1819</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>1074</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>1998</v>
+        <v>1992</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>0</v>
@@ -32591,13 +32606,13 @@
         <v>1334</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>0</v>
@@ -32606,7 +32621,7 @@
         <v>49</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32620,13 +32635,13 @@
         <v>722</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>0</v>
@@ -32635,7 +32650,7 @@
         <v>49</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32643,31 +32658,31 @@
         <v>17</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>1334</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>1966</v>
+        <v>1959</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>51</v>
+      <c r="H68" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>17</v>
       </c>
@@ -32699,19 +32714,19 @@
         <v>17</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G70" s="5" t="n">
         <v>0</v>
@@ -32720,7 +32735,7 @@
         <v>49</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32734,7 +32749,7 @@
         <v>1334</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
@@ -32749,7 +32764,7 @@
         <v>49</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>2030</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32763,7 +32778,7 @@
         <v>1334</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>2085</v>
+        <v>2079</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>0</v>
@@ -32778,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32786,13 +32801,13 @@
         <v>23</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>2088</v>
+        <v>2082</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
@@ -32840,13 +32855,13 @@
         <v>23</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>722</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>2088</v>
+        <v>2082</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0</v>
@@ -32891,58 +32906,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2090</v>
+        <v>2084</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2091</v>
+        <v>2085</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2092</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>2093</v>
+        <v>2087</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2098</v>
+        <v>2092</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>2099</v>
+        <v>2093</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2100</v>
+        <v>2094</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32950,13 +32965,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2102</v>
+        <v>2096</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32964,13 +32979,13 @@
         <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2105</v>
+        <v>2099</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32978,10 +32993,10 @@
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2106</v>
+        <v>2100</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2107</v>
+        <v>2101</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>1337</v>
@@ -32989,72 +33004,72 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>2108</v>
+        <v>2102</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2109</v>
+        <v>2103</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2110</v>
+        <v>2104</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>2111</v>
+        <v>2105</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2112</v>
+        <v>2106</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2113</v>
+        <v>2107</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>2114</v>
+        <v>2108</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2115</v>
+        <v>2109</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>2116</v>
+        <v>2110</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>2117</v>
+        <v>2111</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>2118</v>
+        <v>2112</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>2119</v>
+        <v>2113</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>2120</v>
+        <v>2114</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>2121</v>
+        <v>2115</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2122</v>
+        <v>2116</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
   </sheetData>
@@ -33082,10 +33097,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>2123</v>
+        <v>2117</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2124</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33093,7 +33108,7 @@
         <v>82</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2125</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33101,7 +33116,7 @@
         <v>341</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2126</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33109,7 +33124,7 @@
         <v>694</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2127</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33117,15 +33132,15 @@
         <v>83</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2128</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>2129</v>
+        <v>2123</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2130</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33133,15 +33148,15 @@
         <v>1348</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2131</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2132</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33149,7 +33164,7 @@
         <v>65</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2133</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33157,15 +33172,15 @@
         <v>67</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2134</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>2135</v>
+        <v>2129</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>2136</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33173,15 +33188,15 @@
         <v>50</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>2137</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>2138</v>
+        <v>2132</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>2139</v>
+        <v>2133</v>
       </c>
     </row>
   </sheetData>
